--- a/output/pdf_financials_xlsx/PTF.xlsx
+++ b/output/pdf_financials_xlsx/PTF.xlsx
@@ -930,16 +930,16 @@
         <v>0.70994</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.577493</v>
+        <v>1.194176</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.537342</v>
+        <v>0.794913</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.502059</v>
+        <v>0.75274</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.689147</v>
+        <v>1.0795</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>2.639586</v>
@@ -991,16 +991,16 @@
         <v>3.098926</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.484743</v>
+        <v>9.86806</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.851916</v>
+        <v>0.594345</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.174651</v>
+        <v>-1.425332</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2.453234</v>
+        <v>2.062881</v>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
@@ -1044,22 +1044,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.164941</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.177335</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000214</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000225</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.627733</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.725938</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.839911</v>
       </c>
     </row>
     <row r="13">
@@ -2041,22 +2041,22 @@
         <v>3.346006</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.139347</v>
+        <v>0.974406</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.098926</v>
+        <v>2.921591</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.86806</v>
+        <v>9.86787</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.594345</v>
+        <v>0.594131</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.425332</v>
+        <v>-1.425557</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.062881</v>
+        <v>1.435148</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.029528</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>55.473592</v>
+        <v>54.747654</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2155,22 +2155,22 @@
         <v>3.346006</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.139347</v>
+        <v>0.974406</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.058984</v>
+        <v>2.881649</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.741934</v>
+        <v>4.741744</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.133065</v>
+        <v>-0.133279</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.425332</v>
+        <v>-1.425557</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.062881</v>
+        <v>1.435148</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>1.029528</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>55.473592</v>
+        <v>54.747654</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
         <v>81.57514346935587</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>62.09527058806859</v>
+        <v>53.10586171959689</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80.3121979087739</v>
+        <v>75.65635021027256</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>42.86596308377438</v>
+        <v>42.86424552866166</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-9.578134514971302</v>
+        <v>-9.593538421229173</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>211.9162880319718</v>
+        <v>211.9497407046174</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>65.64706825811383</v>
+        <v>45.67071911394576</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>11.40098390196063</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>84.87672434941928</v>
+        <v>83.76601135429235</v>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
@@ -2411,40 +2411,40 @@
         <v>1.043197</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.385789</v>
+        <v>1.043197</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.382554</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.407498</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.322426</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.307878</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.017653</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.199875</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>10.008858</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.552667</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.102966</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>15.10478</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>4.728836</v>
       </c>
     </row>
     <row r="35">
@@ -2521,40 +2521,40 @@
         <v>1.043197</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.385789</v>
+        <v>1.043197</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.382554</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.407498</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.322426</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.307878</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.017653</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.199875</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>10.008858</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.552667</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.102966</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>15.10478</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>4.728836</v>
       </c>
     </row>
     <row r="37">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -51466,7 +51466,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -61294,7 +61294,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -62442,7 +62442,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -62818,7 +62818,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">

--- a/output/pdf_financials_xlsx/PTF.xlsx
+++ b/output/pdf_financials_xlsx/PTF.xlsx
@@ -744,52 +744,52 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.731985</v>
+        <v>0.785985</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.813813</v>
+        <v>0.860313</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.572487</v>
+        <v>0.6109869999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.446179</v>
+        <v>0.480679</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.444708</v>
+        <v>0.477708</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.395216</v>
+        <v>0.429216</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.428394</v>
+        <v>0.458894</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.577493</v>
+        <v>0.888993</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.537342</v>
+        <v>0.563233</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.502059</v>
+        <v>0.526901</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.689147</v>
+        <v>0.727688</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.046132</v>
+        <v>1.104803</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.836821</v>
+        <v>0.891386</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.887713</v>
+        <v>0.946689</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.954005</v>
+        <v>2.031794</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2.362527</v>
+        <v>2.430344</v>
       </c>
     </row>
     <row r="8">
@@ -7397,19 +7397,19 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.707307</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.552252</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-1.370083</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-2.303971</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-2.79776</v>
       </c>
     </row>
     <row r="122">
@@ -20670,7 +20670,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -27630,7 +27634,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -52326,7 +52334,11 @@
           <t>Directors' fees 13,669</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -54340,7 +54352,11 @@
           <t>Directors' fees 20,504</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -57014,7 +57030,11 @@
           <t>Directors' fees 16,909</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -59492,7 +59512,11 @@
           <t>Directors' fees 13,641</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -62278,7 +62302,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
@@ -72478,7 +72506,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E688" s="5" t="n">
         <v>0.054</v>
       </c>
